--- a/firmValue.xlsx
+++ b/firmValue.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="6000" windowWidth="20640" windowHeight="11760"/>
@@ -12,7 +12,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -88,12 +88,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="2023"/>
@@ -255,7 +255,7 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="L2">
-            <v>268200</v>
+            <v>338750</v>
           </cell>
         </row>
       </sheetData>
@@ -519,16 +519,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J22"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.140625" style="1" customWidth="1"/>
@@ -536,7 +536,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="22.5" customHeight="1">
+    <row r="2" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
@@ -544,17 +544,17 @@
         <v>45221</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="22.5" customHeight="1">
+    <row r="4" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(C7:C10)</f>
-        <v>268200</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="9" customHeight="1"/>
-    <row r="6" spans="2:10" ht="22.5" customHeight="1">
+        <v>338750</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
@@ -562,16 +562,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="22.5" customHeight="1">
+    <row r="7" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="3">
         <f>'[1]2023'!$L$2</f>
-        <v>268200</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="22.5" customHeight="1">
+        <v>338750</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>1</v>
       </c>
@@ -580,7 +580,7 @@
         <v>10300</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="22.5" customHeight="1">
+    <row r="9" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
@@ -592,7 +592,7 @@
         <v>-7900</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="22.5" customHeight="1">
+    <row r="10" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
@@ -604,7 +604,7 @@
         <v>-1950</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C11" s="4"/>
       <c r="G11" s="1" t="s">
         <v>12</v>
@@ -617,7 +617,7 @@
         <v>-37050</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
@@ -625,7 +625,7 @@
         <v>-17200</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="22.5" customHeight="1">
+    <row r="13" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
@@ -637,18 +637,18 @@
         <v>-22600</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J14" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="22.5" customHeight="1">
+    <row r="15" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="9">
         <f>C4+C13</f>
-        <v>265100</v>
+        <v>335650</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>14</v>
@@ -657,7 +657,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G16" s="1" t="s">
         <v>15</v>
       </c>
@@ -665,7 +665,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="7:9">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G17" s="1" t="s">
         <v>16</v>
       </c>
@@ -673,7 +673,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="7:9">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G18" s="1" t="s">
         <v>17</v>
       </c>
@@ -685,7 +685,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="19" spans="7:9">
+    <row r="19" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G19" s="1" t="s">
         <v>18</v>
       </c>
@@ -693,7 +693,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="20" spans="7:9">
+    <row r="20" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G20" s="1" t="s">
         <v>19</v>
       </c>
@@ -701,7 +701,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="7:9">
+    <row r="21" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G21" s="1" t="s">
         <v>15</v>
       </c>
@@ -709,7 +709,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="7:9">
+    <row r="22" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G22" s="1" t="s">
         <v>20</v>
       </c>
